--- a/api/src/excelreports/reportTemplates/Sites.xlsx
+++ b/api/src/excelreports/reportTemplates/Sites.xlsx
@@ -136,9 +136,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
     <t>&lt;state&gt;</t>
   </si>
   <si>
@@ -148,9 +145,6 @@
     <t>Aspect Sites</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>Site ID</t>
   </si>
   <si>
@@ -166,7 +160,13 @@
     <t>&lt;totalDevices&gt;</t>
   </si>
   <si>
-    <t>&lt;issueCategory&gt;</t>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Site Name</t>
+  </si>
+  <si>
+    <t>&lt;siteIssues&gt;</t>
   </si>
 </sst>
 </file>
@@ -789,16 +789,16 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.25" customWidth="1"/>
-    <col min="2" max="2" width="51.25" style="3" customWidth="1"/>
-    <col min="3" max="3" width="30.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="55.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="34.25" style="3" customWidth="1"/>
     <col min="5" max="5" width="26.375" customWidth="1"/>
-    <col min="6" max="6" width="43.875" customWidth="1"/>
+    <col min="6" max="6" width="66.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -816,22 +816,22 @@
     </row>
     <row r="4" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -839,16 +839,16 @@
         <v>33</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>48</v>
